--- a/ASINs to Forecast.xlsx
+++ b/ASINs to Forecast.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gigabyte365-my.sharepoint.com/personal/charleshsu_gigabyteusa_com/Documents/Documents/GitHub/Forecast Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gigabyte365-my.sharepoint.com/personal/charleshsu_gigabyteusa_com/Documents/Laptop/Desktop/VGA Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{45AAEFF9-7462-448C-81ED-DE8115A57EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{705FB532-BBBD-4F49-9642-4DE18AF08D6E}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{5F9174DB-27EE-4AA3-A5C5-99B6EC0CD120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1819998-64D2-4B98-AC29-1021F24198AB}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{134BD2A0-BBF2-4515-A7F2-D8D2375BE721}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{134BD2A0-BBF2-4515-A7F2-D8D2375BE721}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,271 +36,437 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>ASIN</t>
   </si>
   <si>
+    <t>B0DS2QZC9P</t>
+  </si>
+  <si>
+    <t>B0DS2QZ8FN</t>
+  </si>
+  <si>
+    <t>B0DS2QG2KW</t>
+  </si>
+  <si>
+    <t>B07W95D5V3</t>
+  </si>
+  <si>
+    <t>B09YVPZ3RY</t>
+  </si>
+  <si>
+    <t>B09QV67R17</t>
+  </si>
+  <si>
+    <t>B09QNQZMZR</t>
+  </si>
+  <si>
+    <t>B09J2NCD2L</t>
+  </si>
+  <si>
+    <t>B08Z4J6NHW</t>
+  </si>
+  <si>
+    <t>B08Z5M4KFM</t>
+  </si>
+  <si>
+    <t>B08PFX6PZ6</t>
+  </si>
+  <si>
+    <t>B097FYBRXH</t>
+  </si>
+  <si>
+    <t>B0C5S9CHMG</t>
+  </si>
+  <si>
+    <t>B0CSVJZNNX</t>
+  </si>
+  <si>
+    <t>B0CGC5P7H3</t>
+  </si>
+  <si>
+    <t>B0CGHQ32S2</t>
+  </si>
+  <si>
+    <t>B0BRBX747V</t>
+  </si>
+  <si>
+    <t>B0BRBXF3MW</t>
+  </si>
+  <si>
     <t>B07C3DWK1Z</t>
   </si>
   <si>
     <t>B06X9GLGSC</t>
   </si>
   <si>
+    <t>B01KQUDE2Y</t>
+  </si>
+  <si>
+    <t>B08BNRR5SJ</t>
+  </si>
+  <si>
+    <t>B0CS68S77J</t>
+  </si>
+  <si>
+    <t>B07NJQLQWP</t>
+  </si>
+  <si>
+    <t>B09QVPMGYV</t>
+  </si>
+  <si>
+    <t>B0CVHD8PLP</t>
+  </si>
+  <si>
+    <t>B0D4XZXLL7</t>
+  </si>
+  <si>
+    <t>B0C1T7FYQ3</t>
+  </si>
+  <si>
+    <t>B0DQK4XSC7</t>
+  </si>
+  <si>
+    <t>B0971BG25M</t>
+  </si>
+  <si>
+    <t>B0C88SM4LK</t>
+  </si>
+  <si>
+    <t>B0CLF23DXB</t>
+  </si>
+  <si>
+    <t>B09C43DLXG</t>
+  </si>
+  <si>
+    <t>B09BKBJ14W</t>
+  </si>
+  <si>
+    <t>B098PL79LS</t>
+  </si>
+  <si>
+    <t>B0BV89RLW8</t>
+  </si>
+  <si>
+    <t>B0BV8WVT8C</t>
+  </si>
+  <si>
+    <t>B098Q5RC7M</t>
+  </si>
+  <si>
+    <t>B098Q4M4WH</t>
+  </si>
+  <si>
+    <t>B097GMHNCT</t>
+  </si>
+  <si>
+    <t>B097G7RBSZ</t>
+  </si>
+  <si>
+    <t>B097G7KYJ2</t>
+  </si>
+  <si>
+    <t>B09DV9GHT9</t>
+  </si>
+  <si>
+    <t>B098TZ3RMZ</t>
+  </si>
+  <si>
+    <t>B095KWZHJB</t>
+  </si>
+  <si>
+    <t>B0C8K3DFD9</t>
+  </si>
+  <si>
+    <t>B0C8K441T1</t>
+  </si>
+  <si>
+    <t>B0D2JDP1VK</t>
+  </si>
+  <si>
+    <t>B0C8KQRH32</t>
+  </si>
+  <si>
+    <t>B0CDJLSZ73</t>
+  </si>
+  <si>
+    <t>B0C8JZNLZL</t>
+  </si>
+  <si>
+    <t>B0CBVXZSGJ</t>
+  </si>
+  <si>
+    <t>B0C5C1N668</t>
+  </si>
+  <si>
+    <t>B0C5BZZQBG</t>
+  </si>
+  <si>
+    <t>B0C5BQ1HM6</t>
+  </si>
+  <si>
+    <t>B0CBVXZDDL</t>
+  </si>
+  <si>
+    <t>B0C5B9M9JY</t>
+  </si>
+  <si>
+    <t>B0CJ9VSCVF</t>
+  </si>
+  <si>
+    <t>B0CBW16TL3</t>
+  </si>
+  <si>
+    <t>B0BZHFLRLM</t>
+  </si>
+  <si>
+    <t>B0CT3V77VQ</t>
+  </si>
+  <si>
+    <t>B0BZHFLKC2</t>
+  </si>
+  <si>
+    <t>B0BZHBRQCQ</t>
+  </si>
+  <si>
+    <t>B0BZHCQ6PF</t>
+  </si>
+  <si>
+    <t>B0DGGWZPZL</t>
+  </si>
+  <si>
+    <t>B0CSJZ9YK3</t>
+  </si>
+  <si>
+    <t>B0CSJYJP6M</t>
+  </si>
+  <si>
+    <t>B0CVHD8Y97</t>
+  </si>
+  <si>
+    <t>B0CSJWWDS7</t>
+  </si>
+  <si>
+    <t>B0CSJV61BN</t>
+  </si>
+  <si>
+    <t>B0BRR1MPTX</t>
+  </si>
+  <si>
+    <t>B0C5BS1LL9</t>
+  </si>
+  <si>
+    <t>B0C6YJ2HTH</t>
+  </si>
+  <si>
+    <t>B0BRR2R8HH</t>
+  </si>
+  <si>
+    <t>B0CSK2GJXP</t>
+  </si>
+  <si>
+    <t>B0D87BVDWQ</t>
+  </si>
+  <si>
+    <t>B0CSK87B4R</t>
+  </si>
+  <si>
+    <t>B0CSJVCD3Y</t>
+  </si>
+  <si>
+    <t>B0CSK393CR</t>
+  </si>
+  <si>
+    <t>B0C8ZLMKP9</t>
+  </si>
+  <si>
+    <t>B0CSKBG4T3</t>
+  </si>
+  <si>
+    <t>B0CSJYJRKD</t>
+  </si>
+  <si>
+    <t>B0CSK2GHR8</t>
+  </si>
+  <si>
+    <t>B0BXMP9QVF</t>
+  </si>
+  <si>
+    <t>B0BGP8FGNZ</t>
+  </si>
+  <si>
+    <t>B0C8LS7PT2</t>
+  </si>
+  <si>
+    <t>B0C82C1PWN</t>
+  </si>
+  <si>
+    <t>B0DTR54HZZ</t>
+  </si>
+  <si>
+    <t>B0DTR3WM7Y</t>
+  </si>
+  <si>
+    <t>B0DTQNSRZG</t>
+  </si>
+  <si>
+    <t>B0DTQTJQGZ</t>
+  </si>
+  <si>
+    <t>B0DTR3JK3Y</t>
+  </si>
+  <si>
+    <t>B0DTQMLX4F</t>
+  </si>
+  <si>
+    <t>B0DTQVHQ6G</t>
+  </si>
+  <si>
+    <t>B0DTRCBYQC</t>
+  </si>
+  <si>
+    <t>B0DTR7GWG6</t>
+  </si>
+  <si>
+    <t>B0DTQT98M3</t>
+  </si>
+  <si>
+    <t>B0DTRC7782</t>
+  </si>
+  <si>
+    <t>B0DXWQ22CQ</t>
+  </si>
+  <si>
+    <t>B0DTR8FDMN</t>
+  </si>
+  <si>
+    <t>B0DT7JVPVH</t>
+  </si>
+  <si>
+    <t>B0DT7HVT16</t>
+  </si>
+  <si>
+    <t>B0DT7H5JYL</t>
+  </si>
+  <si>
+    <t>B0DT7HKND2</t>
+  </si>
+  <si>
+    <t>B0DT7FT1P5</t>
+  </si>
+  <si>
+    <t>B0DS2R6948</t>
+  </si>
+  <si>
+    <t>B0DS2R7N4F</t>
+  </si>
+  <si>
+    <t>B0DT7GHQMD</t>
+  </si>
+  <si>
+    <t>B0DVCH9WJH</t>
+  </si>
+  <si>
+    <t>B0DVCF7XDF</t>
+  </si>
+  <si>
+    <t>B0DVCGBPL9</t>
+  </si>
+  <si>
+    <t>B0DT7GBNWQ</t>
+  </si>
+  <si>
+    <t>B0DT7GMXHB</t>
+  </si>
+  <si>
+    <t>B01IEO05NU</t>
+  </si>
+  <si>
+    <t>B01HMDS5GS</t>
+  </si>
+  <si>
+    <t>B07TZ4VFB6</t>
+  </si>
+  <si>
     <t>B01M4KGTNI</t>
   </si>
   <si>
-    <t>B01KQUDE2Y</t>
-  </si>
-  <si>
-    <t>B0CS68S77J</t>
-  </si>
-  <si>
-    <t>B08BNRR5SJ</t>
-  </si>
-  <si>
-    <t>B07NJQLQWP</t>
-  </si>
-  <si>
-    <t>B09QVPMGYV</t>
-  </si>
-  <si>
-    <t>B0CVHD8PLP</t>
-  </si>
-  <si>
-    <t>B0D4XZXLL7</t>
-  </si>
-  <si>
-    <t>B0C1T7FYQ3</t>
-  </si>
-  <si>
-    <t>B0971BG25M</t>
-  </si>
-  <si>
-    <t>B0C88SM4LK</t>
-  </si>
-  <si>
-    <t>B0CLF23DXB</t>
-  </si>
-  <si>
-    <t>B09C43DLXG</t>
-  </si>
-  <si>
-    <t>B09BKBJ14W</t>
-  </si>
-  <si>
-    <t>B098PL79LS</t>
-  </si>
-  <si>
-    <t>B0BV89RLW8</t>
-  </si>
-  <si>
-    <t>B098Q5RC7M</t>
-  </si>
-  <si>
-    <t>B098Q4M4WH</t>
-  </si>
-  <si>
-    <t>B097GMHNCT</t>
-  </si>
-  <si>
-    <t>B097G7RBSZ</t>
-  </si>
-  <si>
-    <t>B097G7KYJ2</t>
-  </si>
-  <si>
-    <t>B09DV9GHT9</t>
-  </si>
-  <si>
-    <t>B095KWZHJB</t>
-  </si>
-  <si>
-    <t>B0C8K3DFD9</t>
-  </si>
-  <si>
-    <t>B0C8K441T1</t>
-  </si>
-  <si>
-    <t>B0D2JDP1VK</t>
-  </si>
-  <si>
-    <t>B0C8KQRH32</t>
-  </si>
-  <si>
-    <t>B0CDJLSZ73</t>
-  </si>
-  <si>
-    <t>B0C8JZNLZL</t>
-  </si>
-  <si>
-    <t>B0CBVXZSGJ</t>
-  </si>
-  <si>
-    <t>B0C5C1N668</t>
-  </si>
-  <si>
-    <t>B0C5BZZQBG</t>
-  </si>
-  <si>
-    <t>B0C5BQ1HM6</t>
-  </si>
-  <si>
-    <t>B0D2JFYR6R</t>
-  </si>
-  <si>
-    <t>B0CBVXZDDL</t>
-  </si>
-  <si>
-    <t>B0C5B9M9JY</t>
-  </si>
-  <si>
-    <t>B0CJ9VSCVF</t>
-  </si>
-  <si>
-    <t>B0CBW16TL3</t>
-  </si>
-  <si>
-    <t>B0BZHFLRLM</t>
-  </si>
-  <si>
-    <t>B0CT3V77VQ</t>
-  </si>
-  <si>
-    <t>B0BZHFLKC2</t>
-  </si>
-  <si>
-    <t>B0BZHBRQCQ</t>
-  </si>
-  <si>
-    <t>B0BZHCQ6PF</t>
-  </si>
-  <si>
-    <t>B0CSJZ9YK3</t>
-  </si>
-  <si>
-    <t>B0CSJYJP6M</t>
-  </si>
-  <si>
-    <t>B0CVHD8Y97</t>
-  </si>
-  <si>
-    <t>B0CSJWWDS7</t>
-  </si>
-  <si>
-    <t>B0CSJV61BN</t>
-  </si>
-  <si>
-    <t>B0BRR1MPTX</t>
-  </si>
-  <si>
-    <t>B0C5BS1LL9</t>
-  </si>
-  <si>
-    <t>B0C6YJ2HTH</t>
-  </si>
-  <si>
-    <t>B0BRR2R8HH</t>
-  </si>
-  <si>
-    <t>B0CSK2GJXP</t>
-  </si>
-  <si>
-    <t>B0D87BVDWQ</t>
-  </si>
-  <si>
-    <t>B0CSK87B4R</t>
-  </si>
-  <si>
-    <t>B0CSJVCD3Y</t>
-  </si>
-  <si>
-    <t>B0CSK393CR</t>
-  </si>
-  <si>
-    <t>B0C8ZLMKP9</t>
-  </si>
-  <si>
-    <t>B0CSKBG4T3</t>
-  </si>
-  <si>
-    <t>B0CSJYJRKD</t>
-  </si>
-  <si>
-    <t>B0CSK2GHR8</t>
-  </si>
-  <si>
-    <t>B0BXMP9QVF</t>
-  </si>
-  <si>
-    <t>B0BGP8FGNZ</t>
-  </si>
-  <si>
-    <t>B0C8LS7PT2</t>
-  </si>
-  <si>
-    <t>B0C82C1PWN</t>
-  </si>
-  <si>
-    <t>B01IEO05NU</t>
-  </si>
-  <si>
-    <t>B07TZ4VFB6</t>
-  </si>
-  <si>
-    <t>B07W95D5V3</t>
-  </si>
-  <si>
-    <t>B09QNQZMZR</t>
-  </si>
-  <si>
-    <t>B09J2NCD2L</t>
-  </si>
-  <si>
-    <t>B08Z4J6NHW</t>
-  </si>
-  <si>
-    <t>B08Z5M4KFM</t>
-  </si>
-  <si>
-    <t>B09YVPZ3RY</t>
-  </si>
-  <si>
-    <t>B08PFX6PZ6</t>
-  </si>
-  <si>
-    <t>B097FYBRXH</t>
-  </si>
-  <si>
-    <t>B0C5S9CHMG</t>
-  </si>
-  <si>
-    <t>B0CSVJZNNX</t>
-  </si>
-  <si>
-    <t>B0CGC5P7H3</t>
-  </si>
-  <si>
-    <t>B0CGHQ32S2</t>
-  </si>
-  <si>
-    <t>B0BRBX747V</t>
-  </si>
-  <si>
-    <t>B0BRBXF3MW</t>
-  </si>
-  <si>
-    <t>B0DGGWZPZL</t>
+    <t>B0F5BD1X83</t>
+  </si>
+  <si>
+    <t>B0F5BB8P3Q</t>
+  </si>
+  <si>
+    <t>B0F5B891DJ</t>
+  </si>
+  <si>
+    <t>B0F5BBGCSZ</t>
+  </si>
+  <si>
+    <t>B0F5BCCKY6</t>
+  </si>
+  <si>
+    <t>B0F5BC4N84</t>
+  </si>
+  <si>
+    <t>B0F5B8KQJR</t>
+  </si>
+  <si>
+    <t>B0F91KM1CK</t>
+  </si>
+  <si>
+    <t>B0F91K2KBX</t>
+  </si>
+  <si>
+    <t>B0F8MH9LG2</t>
+  </si>
+  <si>
+    <t>B0F8LGYLD5</t>
+  </si>
+  <si>
+    <t>B0F8L759L4</t>
+  </si>
+  <si>
+    <t>B0F8LNS15L</t>
+  </si>
+  <si>
+    <t>B0F8LDHQ7Y</t>
+  </si>
+  <si>
+    <t>B0F5B74L9N</t>
+  </si>
+  <si>
+    <t>B0F5B89RF5</t>
+  </si>
+  <si>
+    <t>B0F72TVCGF</t>
+  </si>
+  <si>
+    <t>B0F8LXRZ1Y</t>
+  </si>
+  <si>
+    <t>B0F8LPDVPQ</t>
+  </si>
+  <si>
+    <t>B0FBGZYJ6N</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -314,7 +480,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -322,15 +488,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B6E87D82-AC3D-446F-96B0-38454DFF7A7A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -343,10 +528,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -666,432 +847,697 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239AF9F6-03F5-416E-B32F-31827F3AFA12}">
-  <dimension ref="A1:A85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A138"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
